--- a/nr-doc-core-allergy-intolerance/ig/StructureDefinition-fr-core-schedule.xlsx
+++ b/nr-doc-core-allergy-intolerance/ig/StructureDefinition-fr-core-schedule.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-03T09:32:19+00:00</t>
+    <t>2026-09-16T08:22:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-doc-core-allergy-intolerance/ig/StructureDefinition-fr-core-schedule.xlsx
+++ b/nr-doc-core-allergy-intolerance/ig/StructureDefinition-fr-core-schedule.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-16T08:22:23+00:00</t>
+    <t>2026-09-16T15:48:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-doc-core-allergy-intolerance/ig/StructureDefinition-fr-core-schedule.xlsx
+++ b/nr-doc-core-allergy-intolerance/ig/StructureDefinition-fr-core-schedule.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-16T15:48:58+00:00</t>
+    <t>2026-09-17T13:27:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-doc-core-allergy-intolerance/ig/StructureDefinition-fr-core-schedule.xlsx
+++ b/nr-doc-core-allergy-intolerance/ig/StructureDefinition-fr-core-schedule.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-17T13:27:58+00:00</t>
+    <t>2026-10-13T15:20:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-doc-core-allergy-intolerance/ig/StructureDefinition-fr-core-schedule.xlsx
+++ b/nr-doc-core-allergy-intolerance/ig/StructureDefinition-fr-core-schedule.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-13T15:20:13+00:00</t>
+    <t>2026-10-13T15:41:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
